--- a/Riparian/Line Intercept Riparian Survey_FieldForm.xlsx
+++ b/Riparian/Line Intercept Riparian Survey_FieldForm.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franklino\Documents\Restoration_Monitoring_Protocols\Riparian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129C08EA-A616-40B2-AFD0-73FCF24CE20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0132CC-FE05-4C03-A676-F1962D1896E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-4020" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIRS Field Form" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" iterate="1" iterateCount="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,9 +47,6 @@
     <t xml:space="preserve">Transect ID </t>
   </si>
   <si>
-    <t xml:space="preserve">Transect length beyond bank / m </t>
-  </si>
-  <si>
     <t>Staff</t>
   </si>
   <si>
@@ -57,10 +54,6 @@
   </si>
   <si>
     <t>Species (or lowest known taxonomic unit; or notable feature)</t>
-  </si>
-  <si>
-    <t>Height class /
-L-M-C</t>
   </si>
   <si>
     <t>End location / m (1dp)</t>
@@ -79,6 +72,12 @@
   </si>
   <si>
     <t>Start location / m (1dp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transect length / m </t>
+  </si>
+  <si>
+    <t>Height class / L-M-C</t>
   </si>
 </sst>
 </file>
@@ -850,21 +849,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36FB362-6DF6-4339-9550-CB5502D09BDE}">
   <dimension ref="A1:H290"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
-    <col min="2" max="2" width="46.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="25"/>
@@ -878,25 +877,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="40"/>
       <c r="C2" s="27"/>
       <c r="D2" s="39" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
       <c r="G2" s="41"/>
       <c r="H2" s="28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="38"/>
       <c r="C3" s="29"/>
@@ -906,29 +905,29 @@
       <c r="G3" s="30"/>
       <c r="H3" s="31"/>
     </row>
-    <row r="4" spans="1:8" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="31.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="C4" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="F4" s="34" t="s">
         <v>7</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>9</v>
       </c>
       <c r="G4" s="35"/>
       <c r="H4" s="36"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -938,7 +937,7 @@
       <c r="G5" s="17"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -948,7 +947,7 @@
       <c r="G6" s="20"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -958,7 +957,7 @@
       <c r="G7" s="20"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -968,7 +967,7 @@
       <c r="G8" s="20"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -978,7 +977,7 @@
       <c r="G9" s="20"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -988,7 +987,7 @@
       <c r="G10" s="20"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -998,7 +997,7 @@
       <c r="G11" s="20"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1008,7 +1007,7 @@
       <c r="G12" s="20"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1018,7 +1017,7 @@
       <c r="G13" s="20"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1028,7 +1027,7 @@
       <c r="G14" s="20"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1038,7 +1037,7 @@
       <c r="G15" s="20"/>
       <c r="H15" s="21"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1048,7 +1047,7 @@
       <c r="G16" s="20"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1058,7 +1057,7 @@
       <c r="G17" s="20"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1068,7 +1067,7 @@
       <c r="G18" s="20"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -1078,7 +1077,7 @@
       <c r="G19" s="20"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1088,7 +1087,7 @@
       <c r="G20" s="20"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1098,7 +1097,7 @@
       <c r="G21" s="20"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1108,7 +1107,7 @@
       <c r="G22" s="20"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1118,7 +1117,7 @@
       <c r="G23" s="20"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1128,7 +1127,7 @@
       <c r="G24" s="20"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1138,7 +1137,7 @@
       <c r="G25" s="20"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1148,7 +1147,7 @@
       <c r="G26" s="20"/>
       <c r="H26" s="21"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1158,7 +1157,7 @@
       <c r="G27" s="20"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1168,7 +1167,7 @@
       <c r="G28" s="20"/>
       <c r="H28" s="21"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1178,7 +1177,7 @@
       <c r="G29" s="20"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1188,7 +1187,7 @@
       <c r="G30" s="20"/>
       <c r="H30" s="21"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1198,7 +1197,7 @@
       <c r="G31" s="20"/>
       <c r="H31" s="21"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -1208,9 +1207,9 @@
       <c r="G32" s="23"/>
       <c r="H32" s="24"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1220,12 +1219,12 @@
       <c r="G33" s="2"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="G34" s="5"/>
       <c r="H34" s="13"/>
     </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -1235,7 +1234,7 @@
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -1244,7 +1243,7 @@
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -1253,7 +1252,7 @@
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
@@ -1262,7 +1261,7 @@
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
     </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
@@ -1271,7 +1270,7 @@
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
     </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
@@ -1280,7 +1279,7 @@
       <c r="G194" s="5"/>
       <c r="H194" s="5"/>
     </row>
-    <row r="226" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
@@ -1289,7 +1288,7 @@
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
     </row>
-    <row r="258" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
@@ -1298,7 +1297,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="290" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
       <c r="D290" s="5"/>
@@ -1319,7 +1318,7 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="94" orientation="landscape" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LLine Intercept Riparian Survey</oddHeader>
+    <oddHeader>&amp;LLine Intercept Riparian Survey&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
     <oddFooter>&amp;L&amp;9Height: L &lt;1.5m, M 1.5-5m, C &gt;5m
 (print more forms than you think you need)&amp;R&amp;9Record extent of overhanging veg only if part of plant present within 1 m of bankfull.
 Record overhang distance as &amp;"-,Italic"negative value</oddFooter>
@@ -1599,17 +1598,17 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C3322E-64B7-49E6-AA0B-0AD554DEA1CB}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a296c5ae-0ef0-4f95-ad3d-f301a6c58e5e"/>
+    <ds:schemaRef ds:uri="0ab0223f-6664-4c68-9a64-c3dc1c6bff9e"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a296c5ae-0ef0-4f95-ad3d-f301a6c58e5e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0ab0223f-6664-4c68-9a64-c3dc1c6bff9e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
